--- a/ConfigWorkspace/Data/fish.xlsx
+++ b/ConfigWorkspace/Data/fish.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0899BA4B-6233-4011-A81A-D1B4CE4588F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABC1FEDD-E1CD-40B3-AB90-0C6314BC9C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{D81C0305-00CC-4DAF-8474-71B464BE362C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{D81C0305-00CC-4DAF-8474-71B464BE362C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -138,9 +138,6 @@
     <t>普通</t>
   </si>
   <si>
-    <t>Settings/Renderer2D.asset</t>
-  </si>
-  <si>
     <t>最普通的鱼</t>
   </si>
   <si>
@@ -160,6 +157,13 @@
   </si>
   <si>
     <t>深海大型鱼</t>
+  </si>
+  <si>
+    <t>Resources\Icons\sardline.png</t>
+  </si>
+  <si>
+    <t>Resources\Icons\sardline.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -530,7 +534,7 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="24.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.25" style="1" bestFit="1" customWidth="1"/>
@@ -689,7 +693,7 @@
         <v>35</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F5" s="1">
         <v>0.5</v>
@@ -707,7 +711,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -715,13 +719,13 @@
         <v>1002</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -739,7 +743,7 @@
         <v>2</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -747,13 +751,13 @@
         <v>1003</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
@@ -771,7 +775,7 @@
         <v>3</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
